--- a/_downloads/f52a95a041023a4c83e993531fb46e55/Indicadores liquidez-endeuda-renta-H&M.xlsx
+++ b/_downloads/f52a95a041023a4c83e993531fb46e55/Indicadores liquidez-endeuda-renta-H&M.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\migue\Dropbox\UNAL\ADMINISTRACIÓN FINANCIERA\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEF989B-B9C1-45EB-ACEF-1972A0049904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178CFB9A-66B4-43D0-9ACE-B78C556CBB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{88032940-B68D-4784-94D6-624C0E8A8768}"/>
   </bookViews>
   <sheets>
     <sheet name="H&amp;M" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1361,232 +1358,31 @@
           <c:yMode val="edge"/>
           <c:x val="5.0929052891524808E-2"/>
           <c:y val="0.10894489701882197"/>
-          <c:w val="0.87640426694735141"/>
-          <c:h val="0.63397562369303695"/>
+          <c:w val="0.84207987369188109"/>
+          <c:h val="0.6416661089695348"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'H&amp;M'!$G$13</c:f>
+              <c:f>'H&amp;M'!$G$20</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Nivel endeudamiento </c:v>
+                  <c:v> Impacto carga financiera </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="triangle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$12:$K$12</c:f>
-              <c:numCache>
-                <c:formatCode>@</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2020</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$13:$K$13</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.96607989797065008</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.98171631003339987</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.64570785979984358</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.72887987341896388</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-3392-4357-9A4C-BCC187886F3B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'H&amp;M'!$G$15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v> Nivel endeudamiento* </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="star"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$12:$K$12</c:f>
-              <c:numCache>
-                <c:formatCode>@</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2020</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$15:$K$15</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.5755259121438131</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.31356770020416E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.0681006028732594E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-3392-4357-9A4C-BCC187886F3B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1924051535"/>
-        <c:axId val="1924039887"/>
-      </c:scatterChart>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'H&amp;M'!$G$16</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v> Apalancamiento financiero </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="00B0F0"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1597,29 +1393,170 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="00B0F0"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="00B0F0"/>
+                  <a:srgbClr val="C00000"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.3381906750230957E-2"/>
+                  <c:y val="-2.4401284397430858E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-2331-4AF1-A27F-9CD38891ADCC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.5616365815833523E-2"/>
+                  <c:y val="2.4401284397430858E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-2331-4AF1-A27F-9CD38891ADCC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.6974210504550735E-2"/>
+                  <c:y val="2.2172682230206277E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-2331-4AF1-A27F-9CD38891ADCC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.2863470379499129E-2"/>
+                  <c:y val="1.9972255514168508E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-2331-4AF1-A27F-9CD38891ADCC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'H&amp;M'!$I$12:$K$12</c:f>
+              <c:f>'H&amp;M'!$H$12:$K$12</c:f>
               <c:numCache>
                 <c:formatCode>@</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>2020</c:v>
                 </c:pt>
               </c:numCache>
@@ -1627,18 +1564,21 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'H&amp;M'!$I$16:$K$16</c:f>
+              <c:f>'H&amp;M'!$H$20:$K$20</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>37.268829390956121</c:v>
+                  <c:v>7.5577306900659502E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.3114790738256126</c:v>
+                  <c:v>4.1315195576687114E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.2866918819211248</c:v>
+                  <c:v>4.0063729242137393E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.646128426418241E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1646,20 +1586,20 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-3392-4357-9A4C-BCC187886F3B}"/>
+              <c16:uniqueId val="{00000008-2331-4AF1-A27F-9CD38891ADCC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:idx val="2"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'H&amp;M'!$G$17</c:f>
+              <c:f>'H&amp;M'!$G$26</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Apalancamiento financiero* </c:v>
+                  <c:v> Margen Operacional </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1694,9 +1634,136 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.8898987082528304E-2"/>
+                  <c:y val="1.5515297773228619E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000011-2331-4AF1-A27F-9CD38891ADCC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.9453860917888815E-2"/>
+                  <c:y val="-3.1067910378143972E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000012-2331-4AF1-A27F-9CD38891ADCC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.7722059605683212E-2"/>
+                  <c:y val="-2.8830241055556378E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000014-2331-4AF1-A27F-9CD38891ADCC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000013-2331-4AF1-A27F-9CD38891ADCC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'H&amp;M'!$H$12:$K$12</c:f>
+              <c:f>'H&amp;M'!$H$24:$K$24</c:f>
               <c:numCache>
                 <c:formatCode>@</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1717,18 +1784,21 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'H&amp;M'!$I$17:$K$17</c:f>
+              <c:f>'H&amp;M'!$H$26:$K$26</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>10.971459317093037</c:v>
+                  <c:v>-9.9883300506535849E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.6263108000834623</c:v>
+                  <c:v>4.8187378520842192E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.7375927167023382E-2</c:v>
+                  <c:v>9.496780498261749E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.10476956115325309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1736,7 +1806,238 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000010-3392-4357-9A4C-BCC187886F3B}"/>
+              <c16:uniqueId val="{00000009-2331-4AF1-A27F-9CD38891ADCC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'H&amp;M'!$G$28</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Margen EBITDA </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-6.0651123992142543E-2"/>
+                  <c:y val="-2.2196047592103554E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-2331-4AF1-A27F-9CD38891ADCC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.7721279451642534E-2"/>
+                  <c:y val="-2.6629674018891301E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000E-2331-4AF1-A27F-9CD38891ADCC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.1186439383097852E-2"/>
+                  <c:y val="-2.4410534517317083E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000F-2331-4AF1-A27F-9CD38891ADCC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.0241891248773554E-2"/>
+                  <c:y val="-2.8820825163448555E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000010-2331-4AF1-A27F-9CD38891ADCC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'H&amp;M'!$H$24:$K$24</c:f>
+              <c:numCache>
+                <c:formatCode>@</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2020</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'H&amp;M'!$H$28:$K$28</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-5.9110142286888948E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10513845484822026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.16035861874042126</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.19204070490744166</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-2331-4AF1-A27F-9CD38891ADCC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1748,15 +2049,15 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="697901967"/>
-        <c:axId val="697900303"/>
+        <c:axId val="1924051535"/>
+        <c:axId val="1924039887"/>
       </c:scatterChart>
       <c:valAx>
         <c:axId val="1924051535"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="2021"/>
-          <c:min val="2017"/>
+          <c:max val="2020"/>
+          <c:min val="2016"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1804,11 +2105,10 @@
         <c:axId val="1924039887"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="1.2"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1846,67 +2146,6 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
-      <c:valAx>
-        <c:axId val="697900303"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="38"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="r"/>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="697901967"/>
-        <c:crosses val="max"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="697901967"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="@" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="697900303"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1921,10 +2160,10 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="8.1867337831622478E-2"/>
-          <c:y val="0.86083261706890868"/>
-          <c:w val="0.75820418105018739"/>
-          <c:h val="0.13916738293109138"/>
+          <c:x val="8.7589822480416163E-2"/>
+          <c:y val="0.82232450843875848"/>
+          <c:w val="0.67368357005332391"/>
+          <c:h val="7.0891205469587104E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -2127,384 +2366,13 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$12:$K$12</c:f>
-              <c:numCache>
-                <c:formatCode>@</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2020</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$19:$K$19</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>-0.78211495898609673</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.544788990604383</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.002588420345119</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7.2574219372785702</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-2331-4AF1-A27F-9CD38891ADCC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'H&amp;M'!$G$18</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v> Cobertura de intereses </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-2.5452765540871267E-2"/>
-                  <c:y val="2.2191395015742785E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-2.6874770893584258E-2"/>
-                  <c:y val="2.4410534517317065E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-7.0484581497797363E-2"/>
-                  <c:y val="-1.7753116012594227E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$12:$K$12</c:f>
-              <c:numCache>
-                <c:formatCode>@</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2020</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$18:$K$18</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>-1.3216043889712119</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.1663354813702695</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.3704185002012803</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.9593528457372558</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-2331-4AF1-A27F-9CD38891ADCC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$12:$K$12</c:f>
-              <c:numCache>
-                <c:formatCode>@</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2020</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="4"/>
-              <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>1</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000015-2331-4AF1-A27F-9CD38891ADCC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1924051535"/>
-        <c:axId val="1924039887"/>
-      </c:scatterChart>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'H&amp;M'!$G$20</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v> Impacto carga financiera </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-3.9158100832109646E-3"/>
-                  <c:y val="-1.9972255514168546E-2"/>
+                  <c:x val="-7.6265314308494828E-2"/>
+                  <c:y val="2.2144783290628423E-3"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -2516,7 +2384,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-2331-4AF1-A27F-9CD38891ADCC}"/>
+                  <c16:uniqueId val="{00000017-1DB3-4027-B98A-36F8E4DE5701}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2524,8 +2392,8 @@
               <c:idx val="1"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-5.1216155175864433E-2"/>
-                  <c:y val="1.9972255514168508E-2"/>
+                  <c:x val="-3.4666051958406809E-2"/>
+                  <c:y val="-2.8788218277815896E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -2537,7 +2405,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-2331-4AF1-A27F-9CD38891ADCC}"/>
+                  <c16:uniqueId val="{00000018-1DB3-4027-B98A-36F8E4DE5701}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2545,8 +2413,8 @@
               <c:idx val="2"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-3.8707473517788069E-2"/>
-                  <c:y val="1.3314837009445753E-2"/>
+                  <c:x val="-4.67991701438491E-2"/>
+                  <c:y val="-3.1002696606878658E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -2558,7 +2426,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000006-2331-4AF1-A27F-9CD38891ADCC}"/>
+                  <c16:uniqueId val="{00000019-1DB3-4027-B98A-36F8E4DE5701}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2566,8 +2434,8 @@
               <c:idx val="3"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-5.2863470379499129E-2"/>
-                  <c:y val="1.9972255514168508E-2"/>
+                  <c:x val="-4.8532472741769438E-2"/>
+                  <c:y val="-2.4359261619690376E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -2579,7 +2447,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-2331-4AF1-A27F-9CD38891ADCC}"/>
+                  <c16:uniqueId val="{0000001A-1DB3-4027-B98A-36F8E4DE5701}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2659,21 +2527,21 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'H&amp;M'!$H$20:$K$20</c:f>
+              <c:f>'H&amp;M'!$H$19:$K$19</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>7.5577306900659502E-2</c:v>
+                  <c:v>-0.78211495898609673</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.1315195576687114E-2</c:v>
+                  <c:v>2.544788990604383</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.0063729242137393E-2</c:v>
+                  <c:v>4.002588420345119</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.646128426418241E-2</c:v>
+                  <c:v>7.2574219372785702</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2681,41 +2549,49 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-2331-4AF1-A27F-9CD38891ADCC}"/>
+              <c16:uniqueId val="{00000000-1DB3-4027-B98A-36F8E4DE5701}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="3"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'H&amp;M'!$G$26</c:f>
+              <c:f>'H&amp;M'!$G$18</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Margen Operacional </c:v>
+                  <c:v> Cobertura de intereses </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="square"/>
+            <c:symbol val="circle"/>
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
-              <a:ln w="25400">
+              <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -2726,8 +2602,8 @@
               <c:idx val="0"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-7.9698678423472322E-2"/>
-                  <c:y val="6.6574185047226725E-3"/>
+                  <c:x val="-3.8132657154247449E-2"/>
+                  <c:y val="2.4359261619690292E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -2739,7 +2615,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-2331-4AF1-A27F-9CD38891ADCC}"/>
+                  <c16:uniqueId val="{00000016-1DB3-4027-B98A-36F8E4DE5701}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2747,8 +2623,8 @@
               <c:idx val="1"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-2.9453859417370193E-2"/>
-                  <c:y val="-3.10679530220399E-2"/>
+                  <c:x val="-3.7585916193045077E-2"/>
+                  <c:y val="-2.4312705264268347E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -2760,7 +2636,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-2331-4AF1-A27F-9CD38891ADCC}"/>
+                  <c16:uniqueId val="{00000001-1DB3-4027-B98A-36F8E4DE5701}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2768,8 +2644,8 @@
               <c:idx val="2"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-2.5988699485915003E-2"/>
-                  <c:y val="-1.9972255514168546E-2"/>
+                  <c:x val="-2.6874770893584258E-2"/>
+                  <c:y val="2.4410534517317065E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -2781,17 +2657,1419 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-2331-4AF1-A27F-9CD38891ADCC}"/>
+                  <c16:uniqueId val="{00000002-1DB3-4027-B98A-36F8E4DE5701}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
-              <c:delete val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.4085190867324151E-2"/>
+                  <c:y val="2.6536425117066567E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-2331-4AF1-A27F-9CD38891ADCC}"/>
+                  <c16:uniqueId val="{00000003-1DB3-4027-B98A-36F8E4DE5701}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'H&amp;M'!$H$12:$K$12</c:f>
+              <c:numCache>
+                <c:formatCode>@</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2020</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'H&amp;M'!$H$18:$K$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-1.3216043889712119</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1663354813702695</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.3704185002012803</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.9593528457372558</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-1DB3-4027-B98A-36F8E4DE5701}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'H&amp;M'!$H$12:$K$12</c:f>
+              <c:numCache>
+                <c:formatCode>@</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2020</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>1</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-1DB3-4027-B98A-36F8E4DE5701}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1924051535"/>
+        <c:axId val="1924039887"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1924051535"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="2020"/>
+          <c:min val="2016"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="@" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1924039887"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="1"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1924039887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1924051535"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.7589822480416163E-2"/>
+          <c:y val="0.82232450843875848"/>
+          <c:w val="0.67368357005332391"/>
+          <c:h val="7.0891205469587104E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CO"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>Indicadores de Rentabilidad (DuPont)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14879112604497702"/>
+          <c:y val="0.13457616216945215"/>
+          <c:w val="0.80837082768252944"/>
+          <c:h val="0.71636591868704158"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'H&amp;M'!$G$38:$H$38</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> Rotación de Activos </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="40000"/>
+                  <a:lumOff val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'H&amp;M'!$I$36:$K$36</c:f>
+              <c:numCache>
+                <c:formatCode>@</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'H&amp;M'!$I$38:$K$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.81034344327744212</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1379295760936465</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.90538859706285024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-5645-48D0-B35C-9F2A750B5B78}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="1924051535"/>
+        <c:axId val="1924039887"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'H&amp;M'!$G$40:$H$40</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> ROE </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="31750" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.3180841412111032E-2"/>
+                  <c:y val="-2.8985507246376715E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-5645-48D0-B35C-9F2A750B5B78}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.3187660668380541E-2"/>
+                  <c:y val="-2.3715415019762844E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-5645-48D0-B35C-9F2A750B5B78}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.5526992287917736E-2"/>
+                  <c:y val="-2.3715415019762941E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-5645-48D0-B35C-9F2A750B5B78}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'H&amp;M'!$I$36:$K$36</c:f>
+              <c:numCache>
+                <c:formatCode>@</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'H&amp;M'!$I$40:$K$40</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>-0.60580553262894599</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.9555726780071164E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.14425305560235704</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-5645-48D0-B35C-9F2A750B5B78}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1924051535"/>
+        <c:axId val="1924039887"/>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'H&amp;M'!$G$39:$H$39</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> Multiplicador de Capital </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.8080075886067337E-2"/>
+                  <c:y val="-3.1620553359683792E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-5645-48D0-B35C-9F2A750B5B78}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.638479678607956E-2"/>
+                  <c:y val="2.3715415019762844E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-5645-48D0-B35C-9F2A750B5B78}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.6923380741927326E-3"/>
+                  <c:y val="-1.0540184453227932E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000E-5645-48D0-B35C-9F2A750B5B78}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'H&amp;M'!$I$36:$K$36</c:f>
+              <c:numCache>
+                <c:formatCode>@</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'H&amp;M'!$I$39:$K$39</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>38.268829390956121</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.3114790738256126</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.2866918819211248</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000F-5645-48D0-B35C-9F2A750B5B78}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="800558943"/>
+        <c:axId val="800551871"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1924051535"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="@" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1924039887"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1924039887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1924051535"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="800551871"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="800558943"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="800558943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="@" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="800551871"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.17190858854725419"/>
+          <c:y val="0.91068361009329279"/>
+          <c:w val="0.57923128449397998"/>
+          <c:h val="4.4153621113566334E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CO"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14879112604497702"/>
+          <c:y val="8.1875239278279915E-2"/>
+          <c:w val="0.80837082768252944"/>
+          <c:h val="0.76906691614043299"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'H&amp;M'!$G$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Margen Neto </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.6437528171108197E-2"/>
+                  <c:y val="3.1669532994915421E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-0FA0-4FCF-8B18-C51B91FA6AEE}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.9039129406381969E-2"/>
+                  <c:y val="-3.430866074449173E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-0FA0-4FCF-8B18-C51B91FA6AEE}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.6437528171108197E-2"/>
+                  <c:y val="-3.4308660744491702E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-0FA0-4FCF-8B18-C51B91FA6AEE}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2871,21 +4149,21 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'H&amp;M'!$H$26:$K$26</c:f>
+              <c:f>'H&amp;M'!$H$29:$K$29</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-9.9883300506535849E-2</c:v>
+                  <c:v>-0.17217475260548581</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.8187378520842192E-2</c:v>
+                  <c:v>-1.9535248274576918E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.496780498261749E-2</c:v>
+                  <c:v>9.8535487300329908E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.10476956115325309</c:v>
+                  <c:v>4.8476472365310309E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2893,230 +4171,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-2331-4AF1-A27F-9CD38891ADCC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'H&amp;M'!$G$28</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v> Margen EBITDA </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="triangle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:ln w="25400">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-3.4651599314553166E-2"/>
-                  <c:y val="-2.4410534517317145E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-2331-4AF1-A27F-9CD38891ADCC}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-2.7721279451642534E-2"/>
-                  <c:y val="-2.6629674018891301E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-2331-4AF1-A27F-9CD38891ADCC}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-3.1186439383097852E-2"/>
-                  <c:y val="-2.4410534517317083E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-2331-4AF1-A27F-9CD38891ADCC}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-5.7175138869012723E-2"/>
-                  <c:y val="-1.5533976511019971E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-2331-4AF1-A27F-9CD38891ADCC}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$24:$K$24</c:f>
-              <c:numCache>
-                <c:formatCode>@</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2020</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$28:$K$28</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>-5.9110142286888948E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.10513845484822026</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.16035861874042126</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.19204070490744166</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-2331-4AF1-A27F-9CD38891ADCC}"/>
+              <c16:uniqueId val="{00000003-0FA0-4FCF-8B18-C51B91FA6AEE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3128,15 +4183,15 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="2053163599"/>
-        <c:axId val="2053163183"/>
+        <c:axId val="1924051535"/>
+        <c:axId val="1924039887"/>
       </c:scatterChart>
       <c:valAx>
         <c:axId val="1924051535"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2020"/>
-          <c:min val="2016"/>
+          <c:min val="2017"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -3178,17 +4233,16 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
-        <c:minorUnit val="1"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1924039887"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="-1.5"/>
+          <c:min val="-0.22000000000000003"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3226,68 +4280,6 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
-      <c:valAx>
-        <c:axId val="2053163183"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="0.2"/>
-          <c:min val="-0.1"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="r"/>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2053163599"/>
-        <c:crosses val="max"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="2053163599"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="@" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2053163183"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -3298,18 +4290,14 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:legendEntry>
-        <c:idx val="2"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="8.7589822480416163E-2"/>
-          <c:y val="0.82232450843875848"/>
-          <c:w val="0.67368357005332391"/>
-          <c:h val="7.0891205469587104E-2"/>
+          <c:x val="0.17190858854725419"/>
+          <c:y val="0.91068361009329279"/>
+          <c:w val="0.82809141145274578"/>
+          <c:h val="4.4153621113566334E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -4273,8 +5261,9 @@
           <c:h val="0.81495364116070068"/>
         </c:manualLayout>
       </c:layout>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -4291,30 +5280,24 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="25400">
               <a:solidFill>
-                <a:srgbClr val="00B0F0"/>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="00B0F0"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="00B0F0"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
             <c:numRef>
               <c:f>'H&amp;M'!$B$5:$E$5</c:f>
               <c:numCache>
@@ -4334,8 +5317,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
               <c:f>'H&amp;M'!$B$12:$E$12</c:f>
               <c:numCache>
@@ -4355,8 +5338,7 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-30C1-4FB4-94C4-367A3126BEA6}"/>
@@ -4378,30 +5360,22 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="bg2">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="25400">
               <a:solidFill>
-                <a:srgbClr val="C00000"/>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="C00000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
             <c:numRef>
               <c:f>'H&amp;M'!$B$5:$E$5</c:f>
               <c:numCache>
@@ -4421,8 +5395,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
               <c:f>'H&amp;M'!$B$30:$E$30</c:f>
               <c:numCache>
@@ -4442,8 +5416,7 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{0000000A-30C1-4FB4-94C4-367A3126BEA6}"/>
@@ -4458,15 +5431,14 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="1924051535"/>
         <c:axId val="1924039887"/>
-      </c:scatterChart>
-      <c:valAx>
+      </c:barChart>
+      <c:catAx>
         <c:axId val="1924051535"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="2020"/>
-          <c:min val="2017"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -4506,9 +5478,11 @@
         </c:txPr>
         <c:crossAx val="1924039887"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-        <c:majorUnit val="1"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
       <c:valAx>
         <c:axId val="1924039887"/>
         <c:scaling>
@@ -4552,7 +5526,7 @@
         </c:txPr>
         <c:crossAx val="1924051535"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -4570,8 +5544,8 @@
           <c:yMode val="edge"/>
           <c:x val="0.1801348096269457"/>
           <c:y val="0.92689760362604101"/>
-          <c:w val="0.63734377846425616"/>
-          <c:h val="3.4066171021927494E-2"/>
+          <c:w val="0.56349056871884962"/>
+          <c:h val="3.5928704807377365E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -4727,50 +5701,43 @@
           <c:h val="0.81495364116070068"/>
         </c:manualLayout>
       </c:layout>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="2"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'H&amp;M'!$A$12</c:f>
+              <c:f>'H&amp;M'!$G$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Activos corrientes totales </c:v>
+                  <c:v> Razón corriente </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="bg2">
+                <a:lumMod val="90000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="25400">
               <a:solidFill>
-                <a:srgbClr val="00B0F0"/>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="90000"/>
+                </a:schemeClr>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="00B0F0"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="00B0F0"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
             <c:numRef>
-              <c:f>'H&amp;M'!$B$5:$E$5</c:f>
+              <c:f>'H&amp;M'!$H$5:$K$5</c:f>
               <c:numCache>
                 <c:formatCode>@</c:formatCode>
                 <c:ptCount val="4"/>
@@ -4788,76 +5755,69 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'H&amp;M'!$B$12:$E$12</c:f>
+              <c:f>'H&amp;M'!$H$6:$K$6</c:f>
               <c:numCache>
-                <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>123676224</c:v>
+                  <c:v>1.0322158407186912</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>121413091</c:v>
+                  <c:v>1.6901616401264032</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>89743836</c:v>
+                  <c:v>1.2452125365814111</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>172822710</c:v>
+                  <c:v>3.7045146504912112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D67C-4D7C-AE0B-6CB84D105D72}"/>
+              <c16:uniqueId val="{00000003-D67C-4D7C-AE0B-6CB84D105D72}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="3"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'H&amp;M'!$A$30</c:f>
+              <c:f>'H&amp;M'!$G$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Pasivos corrientes totales </c:v>
+                  <c:v> Prueba Ácida </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="25400">
               <a:solidFill>
-                <a:srgbClr val="C00000"/>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="C00000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
             <c:numRef>
-              <c:f>'H&amp;M'!$B$5:$E$5</c:f>
+              <c:f>'H&amp;M'!$H$5:$K$5</c:f>
               <c:numCache>
                 <c:formatCode>@</c:formatCode>
                 <c:ptCount val="4"/>
@@ -4875,32 +5835,111 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'H&amp;M'!$B$30:$E$30</c:f>
+              <c:f>'H&amp;M'!$H$7:$K$7</c:f>
               <c:numCache>
-                <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>119816243</c:v>
+                  <c:v>0.64874610531728993</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>71835195</c:v>
+                  <c:v>1.2940163522908235</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>72071099</c:v>
+                  <c:v>0.66540504675806322</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46651917</c:v>
+                  <c:v>2.109810385712553</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D67C-4D7C-AE0B-6CB84D105D72}"/>
+              <c16:uniqueId val="{00000004-D67C-4D7C-AE0B-6CB84D105D72}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'H&amp;M'!$G$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Liquidez (personalizado) </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'H&amp;M'!$H$5:$K$5</c:f>
+              <c:numCache>
+                <c:formatCode>@</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2020</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'H&amp;M'!$H$9:$K$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.52399618485837252</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2366420667903788</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8927451114886924</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.8066085043670843</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-D67C-4D7C-AE0B-6CB84D105D72}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4912,49 +5951,29 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="1924051535"/>
         <c:axId val="1924039887"/>
-      </c:scatterChart>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'H&amp;M'!$G$6</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v> Razón corriente </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
+          <c:idx val="5"/>
+          <c:order val="3"/>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="triangle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:ln w="25400">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
-          <c:xVal>
+          <c:cat>
             <c:numRef>
               <c:f>'H&amp;M'!$H$5:$K$5</c:f>
               <c:numCache>
@@ -4974,268 +5993,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$6:$K$6</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1.0322158407186912</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.6901616401264032</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.2452125365814111</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.7045146504912112</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-D67C-4D7C-AE0B-6CB84D105D72}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'H&amp;M'!$G$7</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v> Prueba Ácida </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="star"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="38100">
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$5:$K$5</c:f>
-              <c:numCache>
-                <c:formatCode>@</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2020</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$7:$K$7</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.64874610531728993</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.2940163522908235</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.66540504675806322</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.109810385712553</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-D67C-4D7C-AE0B-6CB84D105D72}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'H&amp;M'!$G$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v> Liquidez (personalizado) </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="38100">
-                <a:solidFill>
-                  <a:schemeClr val="accent6">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$5:$K$5</c:f>
-              <c:numCache>
-                <c:formatCode>@</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2020</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$9:$K$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.52399618485837252</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.2366420667903788</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.8927451114886924</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.8066085043670843</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-D67C-4D7C-AE0B-6CB84D105D72}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="dash"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="bg1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$H$5:$K$5</c:f>
-              <c:numCache>
-                <c:formatCode>@</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2020</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numLit>
               <c:formatCode>General</c:formatCode>
               <c:ptCount val="4"/>
@@ -5252,7 +6011,7 @@
                 <c:v>1</c:v>
               </c:pt>
             </c:numLit>
-          </c:yVal>
+          </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -5268,15 +6027,106 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="2133903919"/>
-        <c:axId val="2133915151"/>
-      </c:scatterChart>
-      <c:valAx>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1924051535"/>
+        <c:axId val="1924039887"/>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'H&amp;M'!$G$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Capital de trabajo </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'H&amp;M'!$H$5:$K$5</c:f>
+              <c:numCache>
+                <c:formatCode>@</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2020</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'H&amp;M'!$H$8:$K$8</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3859981</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>49577896</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17672737</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>126170793</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-14A5-4BBC-BC8D-5E6433406D02}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="665507359"/>
+        <c:axId val="665520671"/>
+      </c:lineChart>
+      <c:catAx>
         <c:axId val="1924051535"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="2020"/>
-          <c:min val="2017"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -5316,19 +6166,19 @@
         </c:txPr>
         <c:crossAx val="1924039887"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-        <c:majorUnit val="1"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
       <c:valAx>
         <c:axId val="1924039887"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="175000000.00000003"/>
-          <c:min val="45000000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -5364,18 +6214,16 @@
         </c:txPr>
         <c:crossAx val="1924051535"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="2133915151"/>
+        <c:axId val="665520671"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="5"/>
-          <c:min val="-8"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -5409,12 +6257,12 @@
             <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2133903919"/>
+        <c:crossAx val="665507359"/>
         <c:crosses val="max"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
-      <c:valAx>
-        <c:axId val="2133903919"/>
+      <c:catAx>
+        <c:axId val="665507359"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5424,10 +6272,13 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2133915151"/>
+        <c:crossAx val="665520671"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -5439,7 +6290,7 @@
     <c:legend>
       <c:legendPos val="b"/>
       <c:legendEntry>
-        <c:idx val="5"/>
+        <c:idx val="3"/>
         <c:delete val="1"/>
       </c:legendEntry>
       <c:layout>
@@ -5448,8 +6299,8 @@
           <c:yMode val="edge"/>
           <c:x val="0.1801348096269457"/>
           <c:y val="0.92689760362604101"/>
-          <c:w val="0.80019015638439073"/>
-          <c:h val="6.134151059203248E-2"/>
+          <c:w val="0.81986513428405239"/>
+          <c:h val="3.2107881152935537E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -7521,8 +8372,9 @@
           <c:h val="0.76906691614043299"/>
         </c:manualLayout>
       </c:layout>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -7539,30 +8391,78 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
               <a:solidFill>
-                <a:schemeClr val="accent6"/>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-          </c:marker>
-          <c:xVal>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
             <c:numRef>
               <c:f>'H&amp;M'!$I$24:$K$24</c:f>
               <c:numCache>
@@ -7579,8 +8479,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
               <c:f>'H&amp;M'!$I$31:$K$31</c:f>
               <c:numCache>
@@ -7597,8 +8497,7 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-BD90-4CFB-8A13-4B348C4A1804}"/>
@@ -7620,36 +8519,99 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
               <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="50000"/>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.0546910213885246E-3"/>
+                  <c:y val="-3.1620553359683744E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-4007-4455-AE89-F8F219852DBC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-          </c:marker>
-          <c:xVal>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
             <c:numRef>
               <c:f>'H&amp;M'!$I$24:$K$24</c:f>
               <c:numCache>
@@ -7666,8 +8628,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
               <c:f>'H&amp;M'!$I$32:$K$32</c:f>
               <c:numCache>
@@ -7684,8 +8646,7 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-BD90-4CFB-8A13-4B348C4A1804}"/>
@@ -7707,30 +8668,78 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
               <a:solidFill>
-                <a:srgbClr val="00B0F0"/>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
             <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="00B0F0"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="00B0F0"/>
-                </a:solidFill>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-          </c:marker>
-          <c:xVal>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
             <c:numRef>
               <c:f>'H&amp;M'!$I$24:$K$24</c:f>
               <c:numCache>
@@ -7747,8 +8756,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
               <c:f>'H&amp;M'!$I$33:$K$33</c:f>
               <c:numCache>
@@ -7765,8 +8774,7 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000007-BD90-4CFB-8A13-4B348C4A1804}"/>
@@ -7781,15 +8789,14 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="1924051535"/>
         <c:axId val="1924039887"/>
-      </c:scatterChart>
-      <c:valAx>
+      </c:barChart>
+      <c:catAx>
         <c:axId val="1924051535"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="2020"/>
-          <c:min val="2018"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -7829,9 +8836,11 @@
         </c:txPr>
         <c:crossAx val="1924039887"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-        <c:majorUnit val="1"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
       <c:valAx>
         <c:axId val="1924039887"/>
         <c:scaling>
@@ -7877,7 +8886,7 @@
         </c:txPr>
         <c:crossAx val="1924051535"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -7895,7 +8904,7 @@
           <c:yMode val="edge"/>
           <c:x val="0.17190858854725419"/>
           <c:y val="0.91068361009329279"/>
-          <c:w val="0.46977260490253631"/>
+          <c:w val="0.36415208078721523"/>
           <c:h val="4.4153621113566334E-2"/>
         </c:manualLayout>
       </c:layout>
@@ -8008,7 +9017,7 @@
                 <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t>Indicadores de Rentabilidad (DuPont)</a:t>
+              <a:t>Indicadores de endeudamiento</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -8046,10 +9055,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.14879112604497702"/>
-          <c:y val="8.1875239278279915E-2"/>
-          <c:w val="0.80837082768252944"/>
-          <c:h val="0.76906691614043299"/>
+          <c:x val="5.0929052891524808E-2"/>
+          <c:y val="0.10894489701882197"/>
+          <c:w val="0.87640426694735141"/>
+          <c:h val="0.63397562369303695"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -8060,11 +9069,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'H&amp;M'!$G$37:$H$37</c:f>
+              <c:f>'H&amp;M'!$G$13</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Margen Neto </c:v>
+                  <c:v> Nivel endeudamiento </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8072,157 +9081,47 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
+            <c:symbol val="triangle"/>
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-2.056555269922879E-3"/>
-                  <c:y val="-3.9525691699604744E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-D6B8-4DE7-B779-AAD40E0770FB}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="5.1413881748071981E-2"/>
-                  <c:y val="3.4255599472990776E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-D6B8-4DE7-B779-AAD40E0770FB}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.1131105398457585"/>
-                  <c:y val="5.0065876152832672E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-D6B8-4DE7-B779-AAD40E0770FB}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'H&amp;M'!$I$36:$K$36</c:f>
+              <c:f>'H&amp;M'!$H$12:$K$12</c:f>
               <c:numCache>
                 <c:formatCode>@</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>2020</c:v>
                 </c:pt>
               </c:numCache>
@@ -8230,18 +9129,21 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'H&amp;M'!$I$37:$K$37</c:f>
+              <c:f>'H&amp;M'!$H$13:$K$13</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-1.9535248274576918E-2</c:v>
+                  <c:v>0.96607989797065008</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.8535487300329908E-3</c:v>
+                  <c:v>0.98171631003339987</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.8476472365310309E-2</c:v>
+                  <c:v>0.64570785979984358</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.72887987341896388</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8249,7 +9151,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-D6B8-4DE7-B779-AAD40E0770FB}"/>
+              <c16:uniqueId val="{00000004-3392-4357-9A4C-BCC187886F3B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8258,11 +9160,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'H&amp;M'!$G$38:$H$38</c:f>
+              <c:f>'H&amp;M'!$G$15</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Rotación de Activos </c:v>
+                  <c:v> Nivel endeudamiento* </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8270,157 +9172,52 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="C00000"/>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
+            <c:symbol val="star"/>
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="C00000"/>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="C00000"/>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                  </a:schemeClr>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-8.2262210796915161E-3"/>
-                  <c:y val="2.1080368906455864E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000008-D6B8-4DE7-B779-AAD40E0770FB}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-3.9074550128534703E-2"/>
-                  <c:y val="3.1620553359683792E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-D6B8-4DE7-B779-AAD40E0770FB}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-5.9640102827763497E-2"/>
-                  <c:y val="-2.8985507246376812E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-D6B8-4DE7-B779-AAD40E0770FB}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'H&amp;M'!$I$36:$K$36</c:f>
+              <c:f>'H&amp;M'!$H$12:$K$12</c:f>
               <c:numCache>
                 <c:formatCode>@</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>2020</c:v>
                 </c:pt>
               </c:numCache>
@@ -8428,18 +9225,21 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'H&amp;M'!$I$38:$K$38</c:f>
+              <c:f>'H&amp;M'!$H$15:$K$15</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.81034344327744212</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.1379295760936465</c:v>
+                  <c:v>0.5755259121438131</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.90538859706285024</c:v>
+                  <c:v>4.31356770020416E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.0681006028732594E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8447,205 +9247,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-D6B8-4DE7-B779-AAD40E0770FB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'H&amp;M'!$G$40:$H$40</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v> ROE </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-1.6452442159383032E-2"/>
-                  <c:y val="-4.7430830039525688E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-D6B8-4DE7-B779-AAD40E0770FB}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-4.3187660668380541E-2"/>
-                  <c:y val="-2.3715415019762844E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-D6B8-4DE7-B779-AAD40E0770FB}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-5.5526992287917736E-2"/>
-                  <c:y val="-2.3715415019762941E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-D6B8-4DE7-B779-AAD40E0770FB}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$I$36:$K$36</c:f>
-              <c:numCache>
-                <c:formatCode>@</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2020</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'H&amp;M'!$I$40:$K$40</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>-0.60580553262894599</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.9555726780071164E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.14425305560235704</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-D6B8-4DE7-B779-AAD40E0770FB}"/>
+              <c16:uniqueId val="{00000009-3392-4357-9A4C-BCC187886F3B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8668,11 +9270,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'H&amp;M'!$G$39:$H$39</c:f>
+              <c:f>'H&amp;M'!$G$16</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Multiplicador de Capital </c:v>
+                  <c:v> Apalancamiento financiero </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8701,126 +9303,9 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-1.2339331619537276E-2"/>
-                  <c:y val="-1.5810276679841896E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-D6B8-4DE7-B779-AAD40E0770FB}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-6.7866323907455006E-2"/>
-                  <c:y val="2.3715415019762751E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-D6B8-4DE7-B779-AAD40E0770FB}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-7.8149100257069407E-2"/>
-                  <c:y val="-2.6350461133069925E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-D6B8-4DE7-B779-AAD40E0770FB}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'H&amp;M'!$I$36:$K$36</c:f>
+              <c:f>'H&amp;M'!$I$12:$K$12</c:f>
               <c:numCache>
                 <c:formatCode>@</c:formatCode>
                 <c:ptCount val="3"/>
@@ -8838,18 +9323,18 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'H&amp;M'!$I$39:$K$39</c:f>
+              <c:f>'H&amp;M'!$I$16:$K$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>38.268829390956121</c:v>
+                  <c:v>37.268829390956121</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.3114790738256126</c:v>
+                  <c:v>4.3114790738256126</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.2866918819211248</c:v>
+                  <c:v>2.2866918819211248</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8857,7 +9342,97 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-D6B8-4DE7-B779-AAD40E0770FB}"/>
+              <c16:uniqueId val="{0000000C-3392-4357-9A4C-BCC187886F3B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'H&amp;M'!$G$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Apalancamiento financiero* </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'H&amp;M'!$H$12:$K$12</c:f>
+              <c:numCache>
+                <c:formatCode>@</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2020</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'H&amp;M'!$I$17:$K$17</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>10.971459317093037</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.6263108000834623</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.7375927167023382E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000010-3392-4357-9A4C-BCC187886F3B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8869,15 +9444,15 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="2133932623"/>
-        <c:axId val="2133905583"/>
+        <c:axId val="697901967"/>
+        <c:axId val="697900303"/>
       </c:scatterChart>
       <c:valAx>
         <c:axId val="1924051535"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="2020"/>
-          <c:min val="2018"/>
+          <c:max val="2021"/>
+          <c:min val="2017"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -8919,17 +9494,17 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
+        <c:minorUnit val="1"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1924039887"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.2"/>
-          <c:min val="-0.62000000000000011"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -8968,9 +9543,10 @@
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="2133905583"/>
+        <c:axId val="697900303"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="38"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
@@ -9008,12 +9584,12 @@
             <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2133932623"/>
+        <c:crossAx val="697901967"/>
         <c:crosses val="max"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="2133932623"/>
+        <c:axId val="697901967"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9023,7 +9599,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2133905583"/>
+        <c:crossAx val="697900303"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -9041,10 +9617,10 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.17190858854725419"/>
-          <c:y val="0.91068361009329279"/>
-          <c:w val="0.82809141145274578"/>
-          <c:h val="4.4153621113566334E-2"/>
+          <c:x val="8.1867337831622478E-2"/>
+          <c:y val="0.86083261706890868"/>
+          <c:w val="0.68804968568811264"/>
+          <c:h val="0.12939030673866475"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -9198,6 +9774,86 @@
 </file>
 
 <file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -11105,6 +11761,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -18743,8 +20431,8 @@
       <xdr:row>27</xdr:row>
       <xdr:rowOff>146253</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="CuadroTexto 9">
@@ -18986,7 +20674,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="13" name="CuadroTexto 9">
@@ -19174,8 +20862,8 @@
       <xdr:row>33</xdr:row>
       <xdr:rowOff>13223</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="CuadroTexto 9">
@@ -19461,7 +21149,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="14" name="CuadroTexto 9">
@@ -19649,8 +21337,8 @@
       <xdr:row>36</xdr:row>
       <xdr:rowOff>24897</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="CuadroTexto 24">
@@ -19888,7 +21576,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="15" name="CuadroTexto 24">
@@ -20096,8 +21784,8 @@
       <xdr:row>39</xdr:row>
       <xdr:rowOff>10371</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="CuadroTexto 26">
@@ -20335,7 +22023,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="CuadroTexto 26">
@@ -20543,8 +22231,8 @@
       <xdr:row>41</xdr:row>
       <xdr:rowOff>101097</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="CuadroTexto 25">
@@ -20760,7 +22448,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="CuadroTexto 25">
@@ -20968,8 +22656,8 @@
       <xdr:row>43</xdr:row>
       <xdr:rowOff>189739</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="CuadroTexto 19">
@@ -21426,7 +23114,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="CuadroTexto 19">
@@ -21818,8 +23506,8 @@
       <xdr:row>46</xdr:row>
       <xdr:rowOff>45253</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="CuadroTexto 18">
@@ -22147,7 +23835,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="CuadroTexto 18">
@@ -22412,16 +24100,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>565006</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>513051</xdr:colOff>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>48781</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>1026102</xdr:colOff>
-      <xdr:row>113</xdr:row>
-      <xdr:rowOff>9093</xdr:rowOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>645102</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>17319</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22451,15 +24139,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>494437</xdr:colOff>
-      <xdr:row>113</xdr:row>
-      <xdr:rowOff>136815</xdr:rowOff>
+      <xdr:colOff>719574</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>84861</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>454603</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>148938</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>103909</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>173182</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22488,16 +24176,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>899794</xdr:colOff>
-      <xdr:row>131</xdr:row>
-      <xdr:rowOff>42920</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>761249</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>146829</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>113260</xdr:colOff>
-      <xdr:row>161</xdr:row>
-      <xdr:rowOff>63659</xdr:rowOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>167568</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22526,16 +24214,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>847932</xdr:colOff>
-      <xdr:row>162</xdr:row>
-      <xdr:rowOff>181182</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>33978</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>59955</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>70057</xdr:colOff>
-      <xdr:row>188</xdr:row>
-      <xdr:rowOff>40378</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>156648</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>109651</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22564,16 +24252,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>112260</xdr:colOff>
-      <xdr:row>163</xdr:row>
-      <xdr:rowOff>10206</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>448436</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>68273</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>667885</xdr:colOff>
-      <xdr:row>188</xdr:row>
-      <xdr:rowOff>67356</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>533414</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>125423</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22602,44 +24290,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>23813</xdr:colOff>
-      <xdr:row>163</xdr:row>
-      <xdr:rowOff>23813</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>103188</xdr:colOff>
-      <xdr:row>188</xdr:row>
-      <xdr:rowOff>80963</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="32" name="Gráfico 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>647699</xdr:colOff>
       <xdr:row>23</xdr:row>
@@ -22651,8 +24301,8 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>18289</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="33" name="CuadroTexto 9">
@@ -22938,7 +24588,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="33" name="CuadroTexto 9">
@@ -23126,8 +24776,8 @@
       <xdr:row>22</xdr:row>
       <xdr:rowOff>82242</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="34" name="CuadroTexto 9">
@@ -23433,7 +25083,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="34" name="CuadroTexto 9">
@@ -23629,8 +25279,8 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>51003</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="35" name="CuadroTexto 9">
@@ -23872,7 +25522,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="35" name="CuadroTexto 9">
@@ -24049,16 +25699,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>460815</xdr:colOff>
-      <xdr:row>113</xdr:row>
-      <xdr:rowOff>173183</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>183724</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>86592</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>521805</xdr:colOff>
-      <xdr:row>130</xdr:row>
-      <xdr:rowOff>76804</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>103910</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -24066,6 +25716,44 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6C21D02-43DD-4F73-A694-C1DD887F61A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>99428</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>125710</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>571537</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>145695</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="37" name="Gráfico 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8664C444-4C5A-454B-85A8-FC47C186FE37}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24087,23 +25775,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>99428</xdr:colOff>
-      <xdr:row>131</xdr:row>
-      <xdr:rowOff>21801</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>59085</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>148733</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>277128</xdr:colOff>
-      <xdr:row>161</xdr:row>
-      <xdr:rowOff>41786</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>528138</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>168718</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="37" name="Gráfico 36">
+        <xdr:cNvPr id="38" name="Gráfico 37">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8664C444-4C5A-454B-85A8-FC47C186FE37}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3CC6F90-907D-4411-BA8C-5AF01DB1ABA0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24123,99 +25811,83 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>649941</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>80479</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>291353</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>137629</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="40" name="Gráfico 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78CB6BEC-74BC-4209-B58E-DD0AEC261253}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>165033</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>80478</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>253067</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>130174</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="41" name="Gráfico 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB40C6C2-7AB4-4789-BD9E-DEDA941E0318}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="H&amp;M"/>
-      <sheetName val="Hoja2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="58">
-          <cell r="R58">
-            <v>2017</v>
-          </cell>
-          <cell r="S58">
-            <v>2018</v>
-          </cell>
-          <cell r="T58">
-            <v>2019</v>
-          </cell>
-          <cell r="U58">
-            <v>2020</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="Q59" t="str">
-            <v>Nivel endeudamiento</v>
-          </cell>
-          <cell r="R59">
-            <v>0.96607989797065008</v>
-          </cell>
-          <cell r="S59">
-            <v>0.98171631003339987</v>
-          </cell>
-          <cell r="T59">
-            <v>0.64570785979984358</v>
-          </cell>
-          <cell r="U59">
-            <v>0.72887987341896388</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="Q61" t="str">
-            <v>Nivel endeudamiento*</v>
-          </cell>
-          <cell r="R61">
-            <v>0</v>
-          </cell>
-          <cell r="S61">
-            <v>0.5755259121438131</v>
-          </cell>
-          <cell r="T61">
-            <v>4.31356770020416E-2</v>
-          </cell>
-          <cell r="U61">
-            <v>2.0681006028732594E-2</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="Q62" t="str">
-            <v>Apalancamiento financiero</v>
-          </cell>
-          <cell r="S62">
-            <v>37.268829390956121</v>
-          </cell>
-          <cell r="T62">
-            <v>4.3114790738256126</v>
-          </cell>
-          <cell r="U62">
-            <v>2.2866918819211248</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="Q63" t="str">
-            <v>Apalancamiento financiero*</v>
-          </cell>
-          <cell r="S63">
-            <v>10.971459317093037</v>
-          </cell>
-          <cell r="T63">
-            <v>1.6263108000834623</v>
-          </cell>
-          <cell r="U63">
-            <v>9.7375927167023382E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/_downloads/f52a95a041023a4c83e993531fb46e55/Indicadores liquidez-endeuda-renta-H&M.xlsx
+++ b/_downloads/f52a95a041023a4c83e993531fb46e55/Indicadores liquidez-endeuda-renta-H&M.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\migue\Dropbox\UNAL\ADMINISTRACIÓN FINANCIERA\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178CFB9A-66B4-43D0-9ACE-B78C556CBB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE5A964-61B5-419F-AD5C-B040DDF218B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{88032940-B68D-4784-94D6-624C0E8A8768}"/>
   </bookViews>
@@ -21326,2175 +21326,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>229783</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>24897</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="15" name="CuadroTexto 24">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="14792325" y="7115175"/>
-              <a:ext cx="1858558" cy="453522"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr wrap="square">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle>
-              <a:defPPr>
-                <a:defRPr lang="es-CO"/>
-              </a:defPPr>
-              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl1pPr>
-              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl2pPr>
-              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl3pPr>
-              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl4pPr>
-              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl5pPr>
-              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl6pPr>
-              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl7pPr>
-              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl8pPr>
-              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl9pPr>
-            </a:lstStyle>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                      </a:rPr>
-                      <m:t>ROA</m:t>
-                    </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                      </a:rPr>
-                      <m:t> = </m:t>
-                    </m:r>
-                    <m:f>
-                      <m:fPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="es-CO" sz="1200" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:fPr>
-                      <m:num>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Utilidad</m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t> </m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Neta</m:t>
-                        </m:r>
-                      </m:num>
-                      <m:den>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Activos</m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t> </m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Totales</m:t>
-                        </m:r>
-                      </m:den>
-                    </m:f>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="es-CO" sz="1200"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="15" name="CuadroTexto 24">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="14792325" y="7115175"/>
-              <a:ext cx="1858558" cy="453522"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr wrap="square">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle>
-              <a:defPPr>
-                <a:defRPr lang="es-CO"/>
-              </a:defPPr>
-              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl1pPr>
-              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl2pPr>
-              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl3pPr>
-              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl4pPr>
-              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl5pPr>
-              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl6pPr>
-              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl7pPr>
-              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl8pPr>
-              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl9pPr>
-            </a:lstStyle>
-            <a:p>
-              <a:pPr/>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>"ROA = </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-CO" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t> "Utilidad Neta</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-CO" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>/</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>"</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>Activos Totales</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:endParaRPr lang="es-CO" sz="1200"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>266403</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>10371</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="16" name="CuadroTexto 26">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="14754225" y="7734300"/>
-              <a:ext cx="2695278" cy="448521"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr wrap="square">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle>
-              <a:defPPr>
-                <a:defRPr lang="es-CO"/>
-              </a:defPPr>
-              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl1pPr>
-              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl2pPr>
-              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl3pPr>
-              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl4pPr>
-              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl5pPr>
-              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl6pPr>
-              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl7pPr>
-              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl8pPr>
-              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl9pPr>
-            </a:lstStyle>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                      </a:rPr>
-                      <m:t>ROA</m:t>
-                    </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                      </a:rPr>
-                      <m:t>Operacional</m:t>
-                    </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                      </a:rPr>
-                      <m:t> = </m:t>
-                    </m:r>
-                    <m:f>
-                      <m:fPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="es-CO" sz="1200" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:fPr>
-                      <m:num>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>EBIT</m:t>
-                        </m:r>
-                      </m:num>
-                      <m:den>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Activos</m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t> </m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Totales</m:t>
-                        </m:r>
-                      </m:den>
-                    </m:f>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="es-CO" sz="1200"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="16" name="CuadroTexto 26">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="14754225" y="7734300"/>
-              <a:ext cx="2695278" cy="448521"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr wrap="square">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle>
-              <a:defPPr>
-                <a:defRPr lang="es-CO"/>
-              </a:defPPr>
-              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl1pPr>
-              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl2pPr>
-              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl3pPr>
-              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl4pPr>
-              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl5pPr>
-              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl6pPr>
-              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl7pPr>
-              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl8pPr>
-              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl9pPr>
-            </a:lstStyle>
-            <a:p>
-              <a:pPr/>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>"ROA Operacional = </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-CO" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" i="0">
-                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t> "EBIT</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-CO" sz="1200" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>/</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>"</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" i="0">
-                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>Activos Totales</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:endParaRPr lang="es-CO" sz="1200"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>744133</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>101097</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="17" name="CuadroTexto 25">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="14744700" y="8239125"/>
-              <a:ext cx="1658533" cy="453522"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr wrap="square">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle>
-              <a:defPPr>
-                <a:defRPr lang="es-CO"/>
-              </a:defPPr>
-              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl1pPr>
-              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl2pPr>
-              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl3pPr>
-              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl4pPr>
-              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl5pPr>
-              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl6pPr>
-              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl7pPr>
-              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl8pPr>
-              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl9pPr>
-            </a:lstStyle>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                      </a:rPr>
-                      <m:t>ROE</m:t>
-                    </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                      </a:rPr>
-                      <m:t> =</m:t>
-                    </m:r>
-                    <m:f>
-                      <m:fPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="es-CO" sz="1200" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:fPr>
-                      <m:num>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Utilidad</m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t> </m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Neta</m:t>
-                        </m:r>
-                      </m:num>
-                      <m:den>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Patrimonio</m:t>
-                        </m:r>
-                      </m:den>
-                    </m:f>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="es-CO" sz="1200"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="17" name="CuadroTexto 25">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="14744700" y="8239125"/>
-              <a:ext cx="1658533" cy="453522"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr wrap="square">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle>
-              <a:defPPr>
-                <a:defRPr lang="es-CO"/>
-              </a:defPPr>
-              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl1pPr>
-              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl2pPr>
-              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl3pPr>
-              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl4pPr>
-              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl5pPr>
-              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl6pPr>
-              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl7pPr>
-              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl8pPr>
-              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl9pPr>
-            </a:lstStyle>
-            <a:p>
-              <a:pPr/>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>"ROE =</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-CO" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" i="0">
-                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t> "Utilidad Neta</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-CO" sz="1200" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>/</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>"</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" i="0">
-                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>Patrimonio</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:endParaRPr lang="es-CO" sz="1200"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>466724</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>544977</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>189739</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="18" name="CuadroTexto 19">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="14601824" y="8839200"/>
-              <a:ext cx="5412253" cy="361189"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle>
-              <a:defPPr>
-                <a:defRPr lang="es-CO"/>
-              </a:defPPr>
-              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl1pPr>
-              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl2pPr>
-              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl3pPr>
-              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl4pPr>
-              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl5pPr>
-              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl6pPr>
-              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl7pPr>
-              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl8pPr>
-              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl9pPr>
-            </a:lstStyle>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                      </a:rPr>
-                      <m:t>ROE</m:t>
-                    </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                      </a:rPr>
-                      <m:t> = </m:t>
-                    </m:r>
-                    <m:f>
-                      <m:fPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:fPr>
-                      <m:num>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:solidFill>
-                              <a:srgbClr val="14085C"/>
-                            </a:solidFill>
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Utilidad</m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:solidFill>
-                              <a:srgbClr val="14085C"/>
-                            </a:solidFill>
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t> </m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:solidFill>
-                              <a:srgbClr val="14085C"/>
-                            </a:solidFill>
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Neta</m:t>
-                        </m:r>
-                      </m:num>
-                      <m:den>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Ventas</m:t>
-                        </m:r>
-                      </m:den>
-                    </m:f>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                      </a:rPr>
-                      <m:t>× </m:t>
-                    </m:r>
-                    <m:f>
-                      <m:fPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:fPr>
-                      <m:num>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Ventas</m:t>
-                        </m:r>
-                      </m:num>
-                      <m:den>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Activos</m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t> </m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Totales</m:t>
-                        </m:r>
-                      </m:den>
-                    </m:f>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                      </a:rPr>
-                      <m:t>×</m:t>
-                    </m:r>
-                    <m:f>
-                      <m:fPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:fPr>
-                      <m:num>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Activos</m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t> </m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Totales</m:t>
-                        </m:r>
-                      </m:num>
-                      <m:den>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:solidFill>
-                              <a:srgbClr val="14085C"/>
-                            </a:solidFill>
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Patrimonio</m:t>
-                        </m:r>
-                      </m:den>
-                    </m:f>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                      </a:rPr>
-                      <m:t>=</m:t>
-                    </m:r>
-                    <m:f>
-                      <m:fPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="es-MX" sz="1200" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:fPr>
-                      <m:num>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Utilidad</m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t> </m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Neta</m:t>
-                        </m:r>
-                      </m:num>
-                      <m:den>
-                        <m:r>
-                          <m:rPr>
-                            <m:nor/>
-                          </m:rPr>
-                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                          </a:rPr>
-                          <m:t>Patrimonio</m:t>
-                        </m:r>
-                      </m:den>
-                    </m:f>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="es-CO" sz="1200">
-                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-              </a:endParaRPr>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="18" name="CuadroTexto 19">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="14601824" y="8839200"/>
-              <a:ext cx="5412253" cy="361189"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle>
-              <a:defPPr>
-                <a:defRPr lang="es-CO"/>
-              </a:defPPr>
-              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl1pPr>
-              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl2pPr>
-              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl3pPr>
-              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl4pPr>
-              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl5pPr>
-              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl6pPr>
-              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl7pPr>
-              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl8pPr>
-              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-                <a:defRPr sz="1800" kern="1200">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:lvl9pPr>
-            </a:lstStyle>
-            <a:p>
-              <a:pPr/>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>"ROE = " </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:solidFill>
-                    <a:srgbClr val="14085C"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t> "Utilidad Neta</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:solidFill>
-                    <a:srgbClr val="14085C"/>
-                  </a:solidFill>
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" /"</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>Ventas</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>"  "</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>× </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t> "Ventas</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>/"</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>Activos Totales</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t> "</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>×</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t> "Activos Totales</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>/</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:solidFill>
-                    <a:srgbClr val="14085C"/>
-                  </a:solidFill>
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>"</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:solidFill>
-                    <a:srgbClr val="14085C"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>Patrimonio</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:solidFill>
-                    <a:srgbClr val="14085C"/>
-                  </a:solidFill>
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>"  "</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>=" </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" i="0">
-                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t> "Utilidad Neta</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" /</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>"</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>Patrimonio</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                </a:rPr>
-                <a:t>" </a:t>
-              </a:r>
-              <a:endParaRPr lang="es-CO" sz="1200">
-                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-              </a:endParaRPr>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>952500</xdr:colOff>
       <xdr:row>45</xdr:row>
@@ -23506,8 +21337,8 @@
       <xdr:row>46</xdr:row>
       <xdr:rowOff>45253</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="CuadroTexto 18">
@@ -23799,7 +21630,7 @@
                         <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                         <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                       </a:rPr>
-                      <m:t>Apalancamiento</m:t>
+                      <m:t>Multiplicador</m:t>
                     </m:r>
                     <m:r>
                       <m:rPr>
@@ -23821,7 +21652,29 @@
                         <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                         <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                       </a:rPr>
-                      <m:t>financiero</m:t>
+                      <m:t>de</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>Capital</m:t>
                     </m:r>
                   </m:oMath>
                 </m:oMathPara>
@@ -23835,7 +21688,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="CuadroTexto 18">
@@ -23964,7 +21817,7 @@
                   <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                   <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 </a:rPr>
-                <a:t>"ROE = Margen Neto × Rotación de Activos × Apalancamiento financiero</a:t>
+                <a:t>"ROE = Margen Neto × Rotación de Activos × Multiplicador de Capital</a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="es-CO" sz="1200" b="0" i="0">
@@ -24774,7 +22627,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>466725</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>82242</xdr:rowOff>
+      <xdr:rowOff>88627</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
       <mc:Choice Requires="a14">
@@ -24791,8 +22644,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="14792325" y="4343400"/>
-              <a:ext cx="3619500" cy="348942"/>
+              <a:off x="14856802" y="4402015"/>
+              <a:ext cx="3619500" cy="361189"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -24968,9 +22821,9 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
-                            <a:ea typeface="+mn-ea"/>
-                            <a:cs typeface="+mn-cs"/>
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                           </a:rPr>
                           <m:t>Promedio</m:t>
                         </m:r>
@@ -24983,9 +22836,9 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
-                            <a:ea typeface="+mn-ea"/>
-                            <a:cs typeface="+mn-cs"/>
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                           </a:rPr>
                           <m:t> </m:t>
                         </m:r>
@@ -24998,9 +22851,9 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
-                            <a:ea typeface="+mn-ea"/>
-                            <a:cs typeface="+mn-cs"/>
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                           </a:rPr>
                           <m:t>Pasivo</m:t>
                         </m:r>
@@ -25013,9 +22866,9 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
-                            <a:ea typeface="+mn-ea"/>
-                            <a:cs typeface="+mn-cs"/>
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                           </a:rPr>
                           <m:t> </m:t>
                         </m:r>
@@ -25028,9 +22881,9 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
-                            <a:ea typeface="+mn-ea"/>
-                            <a:cs typeface="+mn-cs"/>
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                           </a:rPr>
                           <m:t>Total</m:t>
                         </m:r>
@@ -25097,8 +22950,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="14792325" y="4343400"/>
-              <a:ext cx="3619500" cy="348942"/>
+              <a:off x="14856802" y="4402015"/>
+              <a:ext cx="3619500" cy="361189"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -25220,9 +23073,9 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                   <a:effectLst/>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 </a:rPr>
                 <a:t> "Promedio Pasivo Total</a:t>
               </a:r>
@@ -25885,6 +23738,2370 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>644769</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>128953</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>654293</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>157514</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="32" name="CuadroTexto 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5024BF4C-304A-4A76-B91C-C9243851FE5F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="14844346" y="7778261"/>
+              <a:ext cx="2295524" cy="453522"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr wrap="square">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="es-CO"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>ROA</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t> = </m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-CO" sz="1200" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Utilidad</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t> </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Neta</m:t>
+                        </m:r>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Prom</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>. </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Activos</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t> </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Totales</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="es-CO" sz="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="32" name="CuadroTexto 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5024BF4C-304A-4A76-B91C-C9243851FE5F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="14844346" y="7778261"/>
+              <a:ext cx="2295524" cy="453522"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr wrap="square">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="es-CO"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"ROA = </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> "Utilidad Neta</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>/</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>Prom. Activos Totales</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:endParaRPr lang="es-CO" sz="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>597875</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>183173</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>740020</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>206732</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="39" name="CuadroTexto 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{966EB4B3-8014-4B39-BEC1-0F675D5840B2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="14797452" y="7195038"/>
+              <a:ext cx="3190145" cy="448521"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr wrap="square">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="es-CO"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>ROA</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>Operacional</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t> = </m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-CO" sz="1200" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>EBIT</m:t>
+                        </m:r>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Prom</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>. </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Activos</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t> </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Totales</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="es-CO" sz="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="39" name="CuadroTexto 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{966EB4B3-8014-4B39-BEC1-0F675D5840B2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="14797452" y="7195038"/>
+              <a:ext cx="3190145" cy="448521"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr wrap="square">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="es-CO"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"ROA Operacional = </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> "EBIT</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1200" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>/</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>Prom. A</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>ctivos Totales</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:endParaRPr lang="es-CO" sz="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>530467</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>95249</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123809</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="42" name="CuadroTexto 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB17B0B2-D4BD-4795-8031-A745C077EE99}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="14730044" y="8381999"/>
+              <a:ext cx="2136532" cy="453522"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr wrap="square">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="es-CO"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>ROE</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t> =</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-CO" sz="1200" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Utilidad</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t> </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Neta</m:t>
+                        </m:r>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>P</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>rom</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>. </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Patrimonio</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="es-CO" sz="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="42" name="CuadroTexto 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB17B0B2-D4BD-4795-8031-A745C077EE99}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="14730044" y="8381999"/>
+              <a:ext cx="2136532" cy="453522"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr wrap="square">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="es-CO"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"ROE =</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> "Utilidad Neta</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1200" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>/</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>P</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>rom. P</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>atrimonio</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:endParaRPr lang="es-CO" sz="1200"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>754671</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>125290</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>117231</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>61517</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="43" name="CuadroTexto 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57CF5900-5E1B-4EFF-A592-1D359F66573F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="14954248" y="9049482"/>
+              <a:ext cx="6220560" cy="361189"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="es-CO"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>ROE</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t> = </m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:solidFill>
+                              <a:srgbClr val="14085C"/>
+                            </a:solidFill>
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Utilidad</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:solidFill>
+                              <a:srgbClr val="14085C"/>
+                            </a:solidFill>
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t> </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:solidFill>
+                              <a:srgbClr val="14085C"/>
+                            </a:solidFill>
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Neta</m:t>
+                        </m:r>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Ventas</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>× </m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Ventas</m:t>
+                        </m:r>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Prom</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>. </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Activos</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t> </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Totales</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>×</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Prom</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>. </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Activos</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t> </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Totales</m:t>
+                        </m:r>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:solidFill>
+                              <a:srgbClr val="14085C"/>
+                            </a:solidFill>
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Prom</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:solidFill>
+                              <a:srgbClr val="14085C"/>
+                            </a:solidFill>
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>. </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:solidFill>
+                              <a:srgbClr val="14085C"/>
+                            </a:solidFill>
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Patrimonio</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                    <m:r>
+                      <m:rPr>
+                        <m:nor/>
+                      </m:rPr>
+                      <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                        <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                        <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-MX" sz="1200" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Utilidad</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t> </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Neta</m:t>
+                        </m:r>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Prom</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>. </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                          </a:rPr>
+                          <m:t>Patrimonio</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="es-CO" sz="1200">
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="43" name="CuadroTexto 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57CF5900-5E1B-4EFF-A592-1D359F66573F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="14954248" y="9049482"/>
+              <a:ext cx="6220560" cy="361189"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle>
+              <a:defPPr>
+                <a:defRPr lang="es-CO"/>
+              </a:defPPr>
+              <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl1pPr>
+              <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl2pPr>
+              <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl3pPr>
+              <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl4pPr>
+              <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl5pPr>
+              <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl6pPr>
+              <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl7pPr>
+              <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl8pPr>
+              <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+                <a:defRPr sz="1800" kern="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:lvl9pPr>
+            </a:lstStyle>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"ROE = " </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="14085C"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> "Utilidad Neta</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="14085C"/>
+                  </a:solidFill>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" /"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>Ventas</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"  "</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>× </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> "Ventas</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>/"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>Prom. Activos Totales</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> "</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>×</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> "Prom. Activos Totales</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>/</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="14085C"/>
+                  </a:solidFill>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="14085C"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>Prom. Patrimonio</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="14085C"/>
+                  </a:solidFill>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"  "</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>=" </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t> "Utilidad Neta</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" /</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>"</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>Prom. Patrimonio</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1200" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                </a:rPr>
+                <a:t>" </a:t>
+              </a:r>
+              <a:endParaRPr lang="es-CO" sz="1200">
+                <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
